--- a/output/pdf_financials_xlsx/IFP.xlsx
+++ b/output/pdf_financials_xlsx/IFP.xlsx
@@ -6103,49 +6103,49 @@
         <v>-32.501</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-4.929</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-7.818</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>20.95</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>77.425</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>69.574</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>40.72</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>40.733</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>84.393</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>49.846</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>58.42</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>175.9</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>145.5</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>246.9</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>186.7</v>
       </c>
     </row>
     <row r="92">
@@ -11848,7 +11848,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -19506,7 +19510,11 @@
           <t>Translation reserve 56,759</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -23050,7 +23058,11 @@
           <t>Translation reserve 84,423</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -27434,7 +27446,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -29340,7 +29356,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IFP.xlsx
+++ b/output/pdf_financials_xlsx/IFP.xlsx
@@ -8149,10 +8149,10 @@
         <v>-116.26</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-155.797</v>
+        <v>-165.733</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-197.175</v>
+        <v>-208.813</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -8210,10 +8210,10 @@
         <v>-116.26</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-155.797</v>
+        <v>-165.733</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-197.175</v>
+        <v>-208.813</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -48382,7 +48382,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IFP.xlsx
+++ b/output/pdf_financials_xlsx/IFP.xlsx
@@ -7377,37 +7377,37 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>5.096</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>36.985</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>1.325</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.537</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>2.089</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>1.926</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>12.509</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>41.437</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>2.355</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -49604,7 +49604,11 @@
           <t>Proceeds on disposal of property, plant and equipment 17</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -51652,7 +51656,11 @@
           <t>Proceeds on disposal of property, plant and equipment 15</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -53062,7 +53070,11 @@
           <t>Proceeds on disposal of property, plant and equipment 5,17</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E430" t="inlineStr">
         <is>
           <t>-</t>
@@ -53578,7 +53590,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
           <t>-</t>
@@ -57842,7 +57858,11 @@
           <t>Proceeds on disposal of property, plant and equipment (note 12)</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -59094,7 +59114,11 @@
           <t>Proceeds on disposal of property, plant and equipment (note 13)</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E488" s="5" t="n">
         <v>5.096</v>
       </c>

--- a/output/pdf_financials_xlsx/IFP.xlsx
+++ b/output/pdf_financials_xlsx/IFP.xlsx
@@ -1376,7 +1376,7 @@
         <v>-1.427</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.31</v>
+        <v>-0.458</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0.555</v>
@@ -1385,7 +1385,7 @@
         <v>16.23</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>24.017</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-7.207</v>
@@ -1394,10 +1394,10 @@
         <v>-34.136</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-38.472</v>
+        <v>-39.092</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>34.359</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-89.57299999999999</v>
@@ -1406,7 +1406,7 @@
         <v>-270.079</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-216.661</v>
+        <v>-216.7</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>91.09999999999999</v>
@@ -1631,7 +1631,7 @@
         <v>-13.453</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-8.706</v>
+        <v>-9.474</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>42.239</v>
@@ -1639,10 +1639,8 @@
       <c r="H20" s="3" t="n">
         <v>40.69</v>
       </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="3" t="n">
+        <v>-30.386</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>65.643</v>
@@ -1651,12 +1649,10 @@
         <v>97.15300000000001</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>111.678</v>
-      </c>
-      <c r="M20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>111.058</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>-103.785</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>280.296</v>
@@ -1665,7 +1661,7 @@
         <v>819.011</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>598.239</v>
+        <v>598.2</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>-266.8</v>
@@ -1818,7 +1814,7 @@
         <v>-13.453</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-8.706</v>
+        <v>-9.474</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>42.239</v>
@@ -1827,7 +1823,7 @@
         <v>40.69</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-54.403</v>
+        <v>-30.386</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>65.643</v>
@@ -1836,10 +1832,10 @@
         <v>97.15300000000001</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>111.678</v>
+        <v>111.058</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-138.144</v>
+        <v>-103.785</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>280.296</v>
@@ -1848,7 +1844,7 @@
         <v>819.011</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>598.239</v>
+        <v>598.2</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>-266.8</v>
@@ -2001,7 +1997,7 @@
         <v>53.812</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>51.211765</v>
+        <v>55.729412</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>57.861644</v>
@@ -2010,7 +2006,7 @@
         <v>65.629032</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>123.643182</v>
+        <v>69.059091</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>69.83297899999999</v>
@@ -2019,10 +2015,10 @@
         <v>69.894245</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>70.237736</v>
+        <v>69.84779899999999</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>89.703896</v>
+        <v>67.39285700000001</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>67.056459</v>
@@ -2031,7 +2027,7 @@
         <v>63.785903</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>55.086464</v>
+        <v>55.082873</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>51.406551</v>
@@ -2306,7 +2302,7 @@
         <v>-11.86595709296524</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-3.438331854480923</v>
+        <v>-5.079858030168589</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>1.296910781885311</v>
@@ -2315,7 +2311,7 @@
         <v>66.35322976287816</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-44.14646251125857</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>9.892930679478381</v>
@@ -2324,10 +2320,10 @@
         <v>26.00065504345375</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>25.62237762237762</v>
+        <v>26.03529803529804</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-24.87187282835302</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>24.21749322057269</v>
@@ -2336,7 +2332,7 @@
         <v>24.79859332102948</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>26.58743404098662</v>
+        <v>26.59221990428273</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>-25.45403744062587</v>
@@ -2367,7 +2363,7 @@
         <v>-1.774228646413758</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-1.025205017451801</v>
+        <v>-1.115643502795585</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>3.821766124814743</v>
@@ -2376,7 +2372,7 @@
         <v>2.811719806489552</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>-3.224120305207793</v>
+        <v>-1.800785243351359</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>3.661658983707366</v>
@@ -2385,10 +2381,10 @@
         <v>4.881800265915484</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>5.107458403972986</v>
+        <v>5.079103453038485</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>-7.364455350483869</v>
+        <v>-5.53277738121068</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>12.83636401938259</v>
@@ -2397,7 +2393,7 @@
         <v>24.90041487972866</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>13.0505890052356</v>
+        <v>13.04973821989529</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>-8.046566335917001</v>
@@ -4766,19 +4762,19 @@
         <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>12.239</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="71">
@@ -4827,19 +4823,19 @@
         <v>6.897</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>6.868</v>
+        <v>19.107</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>7.3</v>
+        <v>22.1</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>44.1</v>
+        <v>61.3</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>48</v>
+        <v>68.3</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>45.7</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="72">
@@ -5071,19 +5067,19 @@
         <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>314.774</v>
+        <v>302.535</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>318.6</v>
+        <v>303.8</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>292.1</v>
+        <v>274.9</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>254.2</v>
+        <v>233.9</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>180.2</v>
+        <v>162.1</v>
       </c>
     </row>
     <row r="76">
@@ -5390,19 +5386,19 @@
         <v>0.3535645258036567</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.2282879974180503</v>
+        <v>0.235769172229615</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.3936164964727936</v>
+        <v>0.4009175669675892</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.5187817845584836</v>
+        <v>0.5287216828478964</v>
       </c>
       <c r="R80" s="3" t="n">
-        <v>0.5903425774877651</v>
+        <v>0.6035889070146819</v>
       </c>
       <c r="S80" s="3" t="n">
-        <v>0.6544164037854889</v>
+        <v>0.6686908517350157</v>
       </c>
     </row>
     <row r="81">
@@ -6605,7 +6601,7 @@
         <v>40.69</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-54.403</v>
+        <v>-30.386</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>65.643</v>
@@ -6617,7 +6613,7 @@
         <v>111.678</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>-138.144</v>
+        <v>-103.785</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>280.296</v>
@@ -10840,7 +10836,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -14150,7 +14150,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -56508,7 +56512,11 @@
           <t>Future income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E463" s="5" t="n">
         <v>7.538</v>
       </c>
@@ -64880,7 +64888,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>-</t>
@@ -69164,7 +69176,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D585" t="inlineStr"/>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E585" t="inlineStr">
         <is>
           <t>-</t>
@@ -73818,7 +73834,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E630" t="inlineStr">
         <is>
           <t>-</t>
@@ -76104,7 +76124,11 @@
           <t>Net earnings (loss) $</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E652" t="inlineStr">
         <is>
           <t>-</t>
